--- a/drowning.xlsx
+++ b/drowning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\drowning_project\5icoding\drowning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B115D9C2-EBA4-495B-896A-C76F90F3F46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA05F62B-7522-4B35-AD70-C74C165FF9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="等级表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="177">
   <si>
     <t>level</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -622,10 +622,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>troubled</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dead</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -703,6 +699,38 @@
   </si>
   <si>
     <t>子事件标题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要找到工作 +工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要去工作。+钱+压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要找到爱人 +爱人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你需要一份更好的工作 -8知识+尊重 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要放松 -压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要更多的东西。+东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你需要创造项目。+项目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有JOB之后，就需要更好工作，去工作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -831,7 +859,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -940,37 +968,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -994,7 +991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1083,45 +1080,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1137,25 +1095,58 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1167,32 +1158,15 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1473,18 +1447,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Q22"/>
+  <dimension ref="B2:S22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="8.88671875" style="1"/>
     <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="8.88671875" style="1"/>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="1"/>
-    <col min="17" max="17" width="34.21875" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="1"/>
+    <col min="18" max="18" width="34.21875" customWidth="1"/>
+    <col min="19" max="19" width="35.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1494,31 +1469,32 @@
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="2" t="s">
+      <c r="E2" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="22">
         <v>0</v>
       </c>
@@ -1531,7 +1507,7 @@
       <c r="E3" s="5">
         <v>10000</v>
       </c>
-      <c r="F3" s="69"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1539,18 +1515,17 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="2">
-        <v>1</v>
-      </c>
       <c r="P3" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2">
         <v>30001</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B4" s="22">
         <v>1</v>
       </c>
@@ -1571,18 +1546,17 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>2</v>
       </c>
-      <c r="P4" s="2">
+      <c r="Q4" s="2">
         <v>30002</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="22">
         <v>2</v>
       </c>
@@ -1603,18 +1577,17 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>3</v>
       </c>
-      <c r="P5" s="2">
+      <c r="Q5" s="2">
         <v>30003</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="22">
         <v>3</v>
       </c>
@@ -1635,18 +1608,17 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>4</v>
       </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
         <v>30004</v>
       </c>
-      <c r="Q6" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="22">
         <v>4</v>
       </c>
@@ -1661,7 +1633,7 @@
       </c>
       <c r="F7" s="33"/>
       <c r="G7" s="2">
-        <v>30013</v>
+        <v>30001</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="3"/>
@@ -1669,18 +1641,17 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>5</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>30005</v>
       </c>
-      <c r="Q7" s="14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="22">
         <v>5</v>
       </c>
@@ -1693,32 +1664,34 @@
       <c r="E8" s="5">
         <v>10005</v>
       </c>
-      <c r="F8" s="70">
+      <c r="F8" s="44">
         <v>20005</v>
       </c>
       <c r="G8" s="2">
-        <v>30013</v>
+        <v>30001</v>
       </c>
       <c r="H8" s="2">
-        <v>30014</v>
+        <v>30002</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>6</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>30006</v>
       </c>
-      <c r="Q8" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="S8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" s="22">
         <v>6</v>
       </c>
@@ -1731,131 +1704,129 @@
       <c r="E9" s="5">
         <v>10006</v>
       </c>
-      <c r="F9" s="70">
+      <c r="F9" s="44">
         <v>20006</v>
       </c>
       <c r="G9" s="2">
-        <v>30013</v>
+        <v>30001</v>
       </c>
       <c r="H9" s="2">
-        <v>30014</v>
-      </c>
-      <c r="I9" s="5">
-        <v>30010</v>
-      </c>
-      <c r="J9" s="5">
-        <v>30011</v>
-      </c>
-      <c r="K9" s="5">
-        <v>30012</v>
+        <v>30002</v>
+      </c>
+      <c r="I9" s="2">
+        <v>30003</v>
+      </c>
+      <c r="J9" s="2">
+        <v>30004</v>
+      </c>
+      <c r="K9" s="2">
+        <v>30005</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="2">
+      <c r="Q9" s="64">
+        <v>300016</v>
+      </c>
+      <c r="R9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B10" s="49">
         <v>7</v>
       </c>
-      <c r="P9" s="2">
+      <c r="C10" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="48">
+        <v>10007</v>
+      </c>
+      <c r="F10" s="50">
+        <v>20007</v>
+      </c>
+      <c r="G10" s="2">
+        <v>30001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>30002</v>
+      </c>
+      <c r="I10" s="2">
+        <v>30003</v>
+      </c>
+      <c r="J10" s="2">
+        <v>30004</v>
+      </c>
+      <c r="K10" s="2">
+        <v>30005</v>
+      </c>
+      <c r="L10" s="2">
+        <v>30006</v>
+      </c>
+      <c r="M10" s="2">
         <v>30007</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="54">
+      <c r="N10" s="2">
+        <v>30016</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="2">
         <v>7</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="34">
-        <v>10007</v>
-      </c>
-      <c r="F10" s="72">
-        <v>20007</v>
-      </c>
-      <c r="G10" s="2">
-        <v>30013</v>
-      </c>
-      <c r="H10" s="2">
-        <v>30014</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="Q10" s="2">
+        <v>30007</v>
+      </c>
+      <c r="R10" s="18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" s="49"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="5">
+        <v>30008</v>
+      </c>
+      <c r="H11" s="5">
+        <v>30009</v>
+      </c>
+      <c r="I11" s="5">
         <v>30010</v>
       </c>
-      <c r="J10" s="5">
-        <v>30011</v>
-      </c>
-      <c r="K10" s="5">
-        <v>30012</v>
-      </c>
-      <c r="L10" s="5">
-        <v>30004</v>
-      </c>
-      <c r="M10" s="5">
-        <v>30005</v>
-      </c>
-      <c r="N10" s="43"/>
-      <c r="O10" s="2">
-        <v>8</v>
-      </c>
-      <c r="P10" s="2">
-        <v>30008</v>
-      </c>
-      <c r="Q10" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="54"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="5">
-        <v>30006</v>
-      </c>
-      <c r="H11" s="5">
-        <v>30007</v>
-      </c>
-      <c r="I11" s="5">
-        <v>30007</v>
-      </c>
-      <c r="J11" s="5">
-        <v>30007</v>
-      </c>
+      <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="2">
-        <v>9</v>
-      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
       <c r="P11" s="2">
-        <v>30009</v>
-      </c>
-      <c r="Q11" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="54">
         <v>8</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="Q11" s="2">
+        <v>30008</v>
+      </c>
+      <c r="R11" s="18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B12" s="49">
+        <v>8</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="34">
+      <c r="D12" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="48">
         <v>10008</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="50">
         <v>20008</v>
       </c>
       <c r="G12" s="5">
@@ -1873,29 +1844,28 @@
       <c r="K12" s="5">
         <v>30005</v>
       </c>
-      <c r="L12" s="5">
-        <v>30006</v>
+      <c r="L12" s="2">
+        <v>30016</v>
       </c>
       <c r="M12" s="5">
         <v>30007</v>
       </c>
-      <c r="N12" s="71"/>
-      <c r="O12" s="2">
-        <v>10</v>
-      </c>
       <c r="P12" s="2">
-        <v>30010</v>
-      </c>
-      <c r="Q12" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="54"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="72"/>
+        <v>9</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>30009</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B13" s="49"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="50"/>
       <c r="G13" s="5">
         <v>30008</v>
       </c>
@@ -1917,31 +1887,30 @@
       <c r="M13" s="5">
         <v>30014</v>
       </c>
-      <c r="N13" s="71"/>
-      <c r="O13" s="2">
-        <v>11</v>
-      </c>
       <c r="P13" s="2">
-        <v>30011</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="54">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>30010</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B14" s="49">
         <v>9</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="48">
         <v>10009</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="50">
         <v>20009</v>
       </c>
       <c r="G14" s="5">
@@ -1959,29 +1928,28 @@
       <c r="K14" s="5">
         <v>30005</v>
       </c>
-      <c r="L14" s="5">
-        <v>30006</v>
+      <c r="L14" s="2">
+        <v>30016</v>
       </c>
       <c r="M14" s="5">
         <v>30007</v>
       </c>
-      <c r="N14" s="71"/>
-      <c r="O14" s="2">
-        <v>12</v>
-      </c>
       <c r="P14" s="2">
-        <v>30012</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="54"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="72"/>
+        <v>11</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>30011</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B15" s="49"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="50"/>
       <c r="G15" s="5">
         <v>30008</v>
       </c>
@@ -2003,31 +1971,30 @@
       <c r="M15" s="5">
         <v>30014</v>
       </c>
-      <c r="N15" s="71"/>
-      <c r="O15" s="2">
-        <v>13</v>
-      </c>
       <c r="P15" s="2">
-        <v>30013</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>30012</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="49">
         <v>10</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="48">
         <v>10010</v>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="50">
         <v>20010</v>
       </c>
       <c r="G16" s="5">
@@ -2045,29 +2012,28 @@
       <c r="K16" s="5">
         <v>30005</v>
       </c>
-      <c r="L16" s="5">
-        <v>30006</v>
+      <c r="L16" s="2">
+        <v>30016</v>
       </c>
       <c r="M16" s="5">
         <v>30007</v>
       </c>
-      <c r="N16" s="71"/>
-      <c r="O16" s="2">
-        <v>14</v>
-      </c>
       <c r="P16" s="2">
-        <v>30014</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="54"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="72"/>
+        <v>13</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>30013</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="50"/>
       <c r="G17" s="5">
         <v>30008</v>
       </c>
@@ -2089,32 +2055,34 @@
       <c r="M17" s="5">
         <v>30014</v>
       </c>
-      <c r="N17" s="71"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="73"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="54">
+      <c r="P17" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>30014</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="49">
         <v>11</v>
       </c>
-      <c r="C18" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D18" s="34" t="s">
+      <c r="C18" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="48">
         <v>10011</v>
       </c>
-      <c r="F18" s="72">
+      <c r="F18" s="50">
         <v>20011</v>
       </c>
-      <c r="G18" s="5">
-        <v>30001</v>
-      </c>
-      <c r="H18" s="5">
-        <v>30002</v>
-      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="5">
         <v>30003</v>
       </c>
@@ -2130,16 +2098,13 @@
       <c r="M18" s="5">
         <v>30007</v>
       </c>
-      <c r="N18" s="71"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="72"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="50"/>
       <c r="G19" s="5">
         <v>30008</v>
       </c>
@@ -2157,19 +2122,16 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
-      <c r="N19" s="71"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="21">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2">
         <v>10012</v>
@@ -2182,16 +2144,13 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="71"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="73"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="21">
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>133</v>
@@ -2207,19 +2166,16 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="71"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="73"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="21">
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E22" s="2">
         <v>10014</v>
@@ -2232,7 +2188,6 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="N22" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -2256,13 +2211,13 @@
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:M2"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:M2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2271,13 +2226,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B24FE6A-378A-4913-A323-20D3394C13FD}">
-  <dimension ref="B3:AF100"/>
+  <dimension ref="C3:AF100"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="3.21875" customWidth="1"/>
     <col min="3" max="6" width="6.21875" customWidth="1"/>
-    <col min="7" max="7" width="6.21875" style="51" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="38" customWidth="1"/>
     <col min="8" max="8" width="4.33203125" customWidth="1"/>
     <col min="9" max="9" width="10.109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="43.88671875" style="1" customWidth="1"/>
@@ -2293,76 +2247,72 @@
     <col min="31" max="32" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="38" t="s">
+    <row r="3" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C3" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="38" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B4" s="36"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="52"/>
+    </row>
+    <row r="4" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C4" s="51"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
       <c r="N4" s="30" t="s">
         <v>9</v>
       </c>
@@ -2421,19 +2371,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
+    <row r="5" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C5" s="51"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
       <c r="G5" s="22"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
       <c r="N5" s="30" t="s">
         <v>31</v>
       </c>
@@ -2492,16 +2441,13 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
+    <row r="6" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C6" s="9">
         <v>1</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="48"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22">
         <v>0</v>
@@ -2535,16 +2481,13 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
+    <row r="7" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
-      <c r="F7" s="48"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22">
         <v>1</v>
@@ -2580,16 +2523,13 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
+    <row r="8" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C8" s="6">
         <v>1</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="48"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22">
         <v>2</v>
@@ -2627,16 +2567,13 @@
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
-        <v>4</v>
-      </c>
+    <row r="9" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C9" s="6">
         <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21"/>
-      <c r="F9" s="48"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22">
         <v>3</v>
@@ -2674,17 +2611,16 @@
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
     </row>
-    <row r="10" spans="2:32" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="57"/>
+    <row r="10" spans="3:32" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
@@ -2693,35 +2629,32 @@
       <c r="Q10" s="21"/>
       <c r="R10" s="21"/>
       <c r="S10" s="21"/>
-      <c r="T10" s="52"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="52"/>
-      <c r="Y10" s="52"/>
-      <c r="Z10" s="52"/>
-      <c r="AA10" s="52"/>
-      <c r="AB10" s="52"/>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="52"/>
-      <c r="AF10" s="52"/>
-    </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>5</v>
-      </c>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+    </row>
+    <row r="11" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C11" s="6">
         <v>1</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="21"/>
-      <c r="F11" s="48"/>
+      <c r="F11" s="35"/>
       <c r="G11" s="22"/>
-      <c r="H11" s="61">
+      <c r="H11" s="59">
         <v>4</v>
       </c>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="56" t="s">
         <v>139</v>
       </c>
       <c r="J11" s="2" t="s">
@@ -2754,19 +2687,16 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
-        <v>6</v>
-      </c>
+    <row r="12" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="22">
         <v>1</v>
       </c>
-      <c r="H12" s="62"/>
-      <c r="I12" s="37"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="57"/>
       <c r="J12" s="7" t="s">
         <v>18</v>
       </c>
@@ -2795,17 +2725,16 @@
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
     </row>
-    <row r="13" spans="2:32" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="55"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="57"/>
+    <row r="13" spans="3:32" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
@@ -2814,24 +2743,21 @@
       <c r="Q13" s="21"/>
       <c r="R13" s="21"/>
       <c r="S13" s="21"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="52"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="52"/>
-      <c r="AA13" s="52"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="52"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="52"/>
-      <c r="AF13" s="52"/>
-    </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B14" s="2">
-        <v>7</v>
-      </c>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
+    </row>
+    <row r="14" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C14" s="6">
         <v>1</v>
       </c>
@@ -2839,10 +2765,10 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
-      <c r="H14" s="61">
+      <c r="H14" s="59">
         <v>5</v>
       </c>
-      <c r="I14" s="35" t="s">
+      <c r="I14" s="56" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
@@ -2877,21 +2803,21 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
+    <row r="15" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C15" s="2"/>
       <c r="D15" s="6">
         <v>2</v>
       </c>
       <c r="E15" s="21"/>
-      <c r="F15" s="48"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="22"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="36"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="58"/>
       <c r="J15" s="2" t="s">
         <v>146</v>
       </c>
       <c r="K15" s="26"/>
-      <c r="L15" s="67" t="s">
+      <c r="L15" s="42" t="s">
         <v>147</v>
       </c>
       <c r="M15" s="2"/>
@@ -2915,19 +2841,16 @@
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B16" s="2">
-        <v>8</v>
-      </c>
+    <row r="16" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="D16" s="21"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="22">
         <v>1</v>
       </c>
-      <c r="H16" s="63"/>
-      <c r="I16" s="36"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="58"/>
       <c r="J16" s="7" t="s">
         <v>16</v>
       </c>
@@ -2958,19 +2881,16 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
     </row>
-    <row r="17" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
-        <v>9</v>
-      </c>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C17" s="2"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="22">
         <v>2</v>
       </c>
-      <c r="H17" s="62"/>
-      <c r="I17" s="37"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="57"/>
       <c r="J17" s="7" t="s">
         <v>18</v>
       </c>
@@ -3001,17 +2921,16 @@
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
     </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B18" s="58"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="60"/>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="2"/>
@@ -3034,23 +2953,21 @@
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
     </row>
-    <row r="19" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="22"/>
-      <c r="H19" s="63">
+      <c r="H19" s="61">
         <v>6</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I19" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K19" s="27" t="s">
@@ -3078,25 +2995,23 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
     </row>
-    <row r="20" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
-        <v>11</v>
-      </c>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C20" s="2"/>
       <c r="D20" s="6">
         <v>2</v>
       </c>
       <c r="E20" s="22"/>
-      <c r="F20" s="48"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="22"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="8" t="s">
+      <c r="H20" s="61"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K20" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="L20" s="68" t="s">
+      <c r="L20" s="43" t="s">
         <v>145</v>
       </c>
       <c r="M20" s="8"/>
@@ -3124,19 +3039,16 @@
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
     </row>
-    <row r="21" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
-        <v>12</v>
-      </c>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C21" s="2"/>
       <c r="D21" s="22"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="22">
         <v>1</v>
       </c>
-      <c r="H21" s="63"/>
-      <c r="I21" s="36"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="58"/>
       <c r="J21" s="12" t="s">
         <v>25</v>
       </c>
@@ -3166,19 +3078,16 @@
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
     </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
-        <v>13</v>
-      </c>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="22">
         <v>2</v>
       </c>
-      <c r="H22" s="63"/>
-      <c r="I22" s="36"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="58"/>
       <c r="J22" s="7" t="s">
         <v>16</v>
       </c>
@@ -3209,19 +3118,16 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
     </row>
-    <row r="23" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>14</v>
-      </c>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C23" s="2"/>
       <c r="D23" s="22"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="22">
         <v>3</v>
       </c>
-      <c r="H23" s="63"/>
-      <c r="I23" s="36"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="58"/>
       <c r="J23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3251,19 +3157,16 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B24" s="2">
-        <v>15</v>
-      </c>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" s="22"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="22">
         <v>4</v>
       </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="36"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="58"/>
       <c r="J24" s="10" t="s">
         <v>26</v>
       </c>
@@ -3293,19 +3196,16 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B25" s="2">
-        <v>16</v>
-      </c>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
       <c r="D25" s="22"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="22">
         <v>5</v>
       </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="37"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="57"/>
       <c r="J25" s="11" t="s">
         <v>27</v>
       </c>
@@ -3338,17 +3238,16 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B26" s="40"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="41"/>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="47"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
       <c r="N26" s="2"/>
@@ -3371,10 +3270,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <v>17</v>
-      </c>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C27" s="6">
         <v>1</v>
       </c>
@@ -3382,10 +3278,10 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
-      <c r="H27" s="61">
+      <c r="H27" s="59">
         <v>7</v>
       </c>
-      <c r="I27" s="35" t="s">
+      <c r="I27" s="56" t="s">
         <v>50</v>
       </c>
       <c r="J27" s="2" t="s">
@@ -3416,19 +3312,16 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B28" s="2">
-        <v>18</v>
-      </c>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C28" s="2"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="22">
         <v>1</v>
       </c>
-      <c r="H28" s="63"/>
-      <c r="I28" s="36"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="58"/>
       <c r="J28" s="13" t="s">
         <v>52</v>
       </c>
@@ -3457,17 +3350,16 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B29" s="2">
-        <v>19</v>
-      </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
       <c r="G29" s="22">
         <v>2</v>
       </c>
-      <c r="H29" s="63"/>
-      <c r="I29" s="36"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="58"/>
       <c r="J29" s="14" t="s">
         <v>70</v>
       </c>
@@ -3487,19 +3379,16 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B30" s="2">
-        <v>20</v>
-      </c>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C30" s="2"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="22">
         <v>3</v>
       </c>
-      <c r="H30" s="63"/>
-      <c r="I30" s="36"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="58"/>
       <c r="J30" s="17" t="s">
         <v>72</v>
       </c>
@@ -3528,19 +3417,16 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B31" s="2">
-        <v>21</v>
-      </c>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C31" s="2"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="22">
         <v>4</v>
       </c>
-      <c r="H31" s="63"/>
-      <c r="I31" s="36"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="58"/>
       <c r="J31" s="15" t="s">
         <v>53</v>
       </c>
@@ -3569,19 +3455,16 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B32" s="2">
-        <v>22</v>
-      </c>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C32" s="2"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="22">
         <v>5</v>
       </c>
-      <c r="H32" s="63"/>
-      <c r="I32" s="36"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="58"/>
       <c r="J32" s="18" t="s">
         <v>54</v>
       </c>
@@ -3608,19 +3491,16 @@
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B33" s="2">
-        <v>23</v>
-      </c>
+    <row r="33" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C33" s="2"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
       <c r="G33" s="22">
         <v>6</v>
       </c>
-      <c r="H33" s="63"/>
-      <c r="I33" s="36"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="58"/>
       <c r="J33" s="18" t="s">
         <v>77</v>
       </c>
@@ -3649,19 +3529,16 @@
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
     </row>
-    <row r="34" spans="2:32" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
-        <v>24</v>
-      </c>
+    <row r="34" spans="3:32" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="2"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="48"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="22">
         <v>7</v>
       </c>
-      <c r="H34" s="63"/>
-      <c r="I34" s="36"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="58"/>
       <c r="J34" s="7" t="s">
         <v>18</v>
       </c>
@@ -3690,19 +3567,16 @@
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B35" s="2">
-        <v>25</v>
-      </c>
+    <row r="35" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C35" s="2"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="48"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="35"/>
       <c r="G35" s="22">
         <v>8</v>
       </c>
-      <c r="H35" s="63"/>
-      <c r="I35" s="36"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="58"/>
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
@@ -3733,19 +3607,16 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B36" s="2">
-        <v>26</v>
-      </c>
+    <row r="36" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C36" s="2"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="35"/>
       <c r="G36" s="22">
         <v>9</v>
       </c>
-      <c r="H36" s="63"/>
-      <c r="I36" s="36"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="58"/>
       <c r="J36" s="12" t="s">
         <v>25</v>
       </c>
@@ -3772,19 +3643,16 @@
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B37" s="2">
-        <v>27</v>
-      </c>
+    <row r="37" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C37" s="2"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="48"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="35"/>
       <c r="G37" s="22">
         <v>10</v>
       </c>
-      <c r="H37" s="63"/>
-      <c r="I37" s="36"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="58"/>
       <c r="J37" s="10" t="s">
         <v>26</v>
       </c>
@@ -3813,19 +3681,16 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B38" s="2">
-        <v>28</v>
-      </c>
+    <row r="38" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C38" s="2"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="48"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
       <c r="G38" s="22">
         <v>11</v>
       </c>
-      <c r="H38" s="63"/>
-      <c r="I38" s="36"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="58"/>
       <c r="J38" s="11" t="s">
         <v>27</v>
       </c>
@@ -3854,23 +3719,20 @@
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B39" s="2">
-        <v>29</v>
-      </c>
+    <row r="39" spans="3:32" x14ac:dyDescent="0.25">
       <c r="D39" s="6">
         <v>2</v>
       </c>
       <c r="E39" s="22"/>
-      <c r="F39" s="48"/>
+      <c r="F39" s="35"/>
       <c r="G39" s="22"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="37"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="57"/>
       <c r="J39" s="2" t="s">
         <v>78</v>
       </c>
       <c r="K39" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -3894,17 +3756,16 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B40" s="64"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="66"/>
+    <row r="40" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="63"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -3927,10 +3788,7 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B41" s="2">
-        <v>30</v>
-      </c>
+    <row r="41" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C41" s="6">
         <v>1</v>
       </c>
@@ -3938,17 +3796,17 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="35">
+      <c r="H41" s="56">
         <v>8</v>
       </c>
-      <c r="I41" s="35" t="s">
+      <c r="I41" s="56" t="s">
         <v>79</v>
       </c>
       <c r="J41" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K41" s="26" t="s">
         <v>152</v>
-      </c>
-      <c r="K41" s="26" t="s">
-        <v>153</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -3972,24 +3830,23 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B42" s="2"/>
+    <row r="42" spans="3:32" x14ac:dyDescent="0.25">
       <c r="D42" s="6">
         <v>2</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="48"/>
+      <c r="F42" s="35"/>
       <c r="G42" s="21"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
       <c r="J42" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K42" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="L42" s="42" t="s">
         <v>154</v>
-      </c>
-      <c r="L42" s="67" t="s">
-        <v>155</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -4012,19 +3869,16 @@
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B43" s="2">
-        <v>31</v>
-      </c>
+    <row r="43" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="21">
         <v>1</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
       <c r="J43" s="2" t="s">
         <v>82</v>
       </c>
@@ -4055,19 +3909,16 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B44" s="2">
-        <v>32</v>
-      </c>
+    <row r="44" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="48"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="21">
         <v>2</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="58"/>
       <c r="J44" s="2" t="s">
         <v>91</v>
       </c>
@@ -4098,19 +3949,16 @@
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B45" s="2">
-        <v>33</v>
-      </c>
+    <row r="45" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="48"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="35"/>
       <c r="G45" s="21">
         <v>3</v>
       </c>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
       <c r="J45" s="2" t="s">
         <v>81</v>
       </c>
@@ -4141,19 +3989,16 @@
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B46" s="2">
-        <v>34</v>
-      </c>
+    <row r="46" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="35"/>
       <c r="G46" s="21">
         <v>4</v>
       </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
       <c r="J46" s="13" t="s">
         <v>52</v>
       </c>
@@ -4184,19 +4029,16 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B47" s="2">
-        <v>35</v>
-      </c>
+    <row r="47" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="48"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="35"/>
       <c r="G47" s="21">
         <v>5</v>
       </c>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
       <c r="J47" s="14" t="s">
         <v>70</v>
       </c>
@@ -4227,19 +4069,16 @@
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
-        <v>36</v>
-      </c>
+    <row r="48" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="48"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="35"/>
       <c r="G48" s="21">
         <v>6</v>
       </c>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="58"/>
       <c r="J48" s="17" t="s">
         <v>72</v>
       </c>
@@ -4270,19 +4109,16 @@
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
-    <row r="49" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B49" s="2">
-        <v>37</v>
-      </c>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="48"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="35"/>
       <c r="G49" s="21">
         <v>7</v>
       </c>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
       <c r="J49" s="15" t="s">
         <v>53</v>
       </c>
@@ -4311,19 +4147,16 @@
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
-    <row r="50" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B50" s="2">
-        <v>38</v>
-      </c>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="48"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
       <c r="G50" s="21">
         <v>8</v>
       </c>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
       <c r="J50" s="18" t="s">
         <v>54</v>
       </c>
@@ -4352,19 +4185,16 @@
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B51" s="2">
-        <v>39</v>
-      </c>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="48"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="35"/>
       <c r="G51" s="21">
         <v>9</v>
       </c>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
       <c r="J51" s="18" t="s">
         <v>77</v>
       </c>
@@ -4395,19 +4225,16 @@
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
-    <row r="52" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B52" s="2">
-        <v>40</v>
-      </c>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="48"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="35"/>
       <c r="G52" s="21">
         <v>10</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
       <c r="J52" s="12" t="s">
         <v>25</v>
       </c>
@@ -4436,19 +4263,16 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B53" s="2">
-        <v>41</v>
-      </c>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="48"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="35"/>
       <c r="G53" s="21">
         <v>11</v>
       </c>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="58"/>
       <c r="J53" s="10" t="s">
         <v>26</v>
       </c>
@@ -4479,19 +4303,16 @@
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B54" s="2">
-        <v>42</v>
-      </c>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="48"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="35"/>
       <c r="G54" s="21">
         <v>12</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
       <c r="J54" s="11" t="s">
         <v>27</v>
       </c>
@@ -4522,19 +4343,16 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B55" s="2">
-        <v>43</v>
-      </c>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="48"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="35"/>
       <c r="G55" s="21">
         <v>13</v>
       </c>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="58"/>
       <c r="J55" s="7" t="s">
         <v>18</v>
       </c>
@@ -4563,19 +4381,16 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B56" s="2">
-        <v>44</v>
-      </c>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="48"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="35"/>
       <c r="G56" s="21">
         <v>14</v>
       </c>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
       <c r="J56" s="7" t="s">
         <v>16</v>
       </c>
@@ -4604,17 +4419,16 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B57" s="40"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="41"/>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+      <c r="H57" s="46"/>
+      <c r="I57" s="46"/>
+      <c r="J57" s="46"/>
+      <c r="K57" s="47"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="3"/>
@@ -4637,10 +4451,7 @@
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
-    <row r="58" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B58" s="2">
-        <v>45</v>
-      </c>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C58" s="6">
         <v>1</v>
       </c>
@@ -4648,11 +4459,11 @@
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
       <c r="G58" s="21"/>
-      <c r="H58" s="35">
+      <c r="H58" s="56">
         <v>9</v>
       </c>
-      <c r="I58" s="35" t="s">
-        <v>149</v>
+      <c r="I58" s="56" t="s">
+        <v>134</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>103</v>
@@ -4682,27 +4493,24 @@
       <c r="AE58" s="3"/>
       <c r="AF58" s="3"/>
     </row>
-    <row r="59" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B59" s="2">
-        <v>46</v>
-      </c>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
       <c r="D59" s="6">
         <v>2</v>
       </c>
       <c r="E59" s="2"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
       <c r="J59" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K59" s="26" t="s">
         <v>105</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
@@ -4725,17 +4533,16 @@
       <c r="AE59" s="3"/>
       <c r="AF59" s="3"/>
     </row>
-    <row r="60" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B60" s="2"/>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="52">
-        <v>1</v>
-      </c>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="39">
+        <v>1</v>
+      </c>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
       <c r="J60" s="2" t="s">
         <v>82</v>
       </c>
@@ -4762,17 +4569,16 @@
       <c r="AE60" s="3"/>
       <c r="AF60" s="3"/>
     </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B61" s="2"/>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="52">
+      <c r="E61" s="34"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="39">
         <v>2</v>
       </c>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="58"/>
       <c r="J61" s="2" t="s">
         <v>91</v>
       </c>
@@ -4799,17 +4605,16 @@
       <c r="AE61" s="3"/>
       <c r="AF61" s="3"/>
     </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B62" s="2"/>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="52">
+      <c r="E62" s="34"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="39">
         <v>3</v>
       </c>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
       <c r="J62" s="2" t="s">
         <v>81</v>
       </c>
@@ -4836,17 +4641,16 @@
       <c r="AE62" s="3"/>
       <c r="AF62" s="3"/>
     </row>
-    <row r="63" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B63" s="2"/>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="52">
+      <c r="E63" s="34"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="39">
         <v>4</v>
       </c>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
       <c r="J63" s="13" t="s">
         <v>52</v>
       </c>
@@ -4873,17 +4677,16 @@
       <c r="AE63" s="3"/>
       <c r="AF63" s="3"/>
     </row>
-    <row r="64" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B64" s="2"/>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="52">
+      <c r="E64" s="34"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="39">
         <v>5</v>
       </c>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="58"/>
       <c r="J64" s="14" t="s">
         <v>70</v>
       </c>
@@ -4910,17 +4713,16 @@
       <c r="AE64" s="3"/>
       <c r="AF64" s="3"/>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B65" s="2"/>
+    <row r="65" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="52">
+      <c r="E65" s="34"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="39">
         <v>6</v>
       </c>
-      <c r="H65" s="36"/>
-      <c r="I65" s="36"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
       <c r="J65" s="17" t="s">
         <v>72</v>
       </c>
@@ -4947,17 +4749,16 @@
       <c r="AE65" s="3"/>
       <c r="AF65" s="3"/>
     </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B66" s="2"/>
+    <row r="66" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="52">
+      <c r="E66" s="34"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="39">
         <v>7</v>
       </c>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="58"/>
       <c r="J66" s="15" t="s">
         <v>53</v>
       </c>
@@ -4984,17 +4785,16 @@
       <c r="AE66" s="3"/>
       <c r="AF66" s="3"/>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B67" s="2"/>
+    <row r="67" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="52">
+      <c r="E67" s="34"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="39">
         <v>8</v>
       </c>
-      <c r="H67" s="36"/>
-      <c r="I67" s="36"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
       <c r="J67" s="18" t="s">
         <v>54</v>
       </c>
@@ -5021,17 +4821,16 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
     </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B68" s="2"/>
+    <row r="68" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="52">
+      <c r="E68" s="34"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="39">
         <v>9</v>
       </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
       <c r="J68" s="18" t="s">
         <v>77</v>
       </c>
@@ -5058,17 +4857,16 @@
       <c r="AE68" s="3"/>
       <c r="AF68" s="3"/>
     </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B69" s="2"/>
+    <row r="69" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="52">
+      <c r="E69" s="34"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="39">
         <v>10</v>
       </c>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
+      <c r="H69" s="58"/>
+      <c r="I69" s="58"/>
       <c r="J69" s="12" t="s">
         <v>25</v>
       </c>
@@ -5095,17 +4893,16 @@
       <c r="AE69" s="3"/>
       <c r="AF69" s="3"/>
     </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B70" s="2"/>
+    <row r="70" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="52">
+      <c r="E70" s="34"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="39">
         <v>11</v>
       </c>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
       <c r="J70" s="10" t="s">
         <v>26</v>
       </c>
@@ -5132,17 +4929,16 @@
       <c r="AE70" s="3"/>
       <c r="AF70" s="3"/>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B71" s="2"/>
+    <row r="71" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="52">
+      <c r="E71" s="34"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="39">
         <v>12</v>
       </c>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="H71" s="58"/>
+      <c r="I71" s="58"/>
       <c r="J71" s="11" t="s">
         <v>27</v>
       </c>
@@ -5169,17 +4965,16 @@
       <c r="AE71" s="3"/>
       <c r="AF71" s="3"/>
     </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B72" s="2"/>
+    <row r="72" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="52">
+      <c r="E72" s="34"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="39">
         <v>13</v>
       </c>
-      <c r="H72" s="36"/>
-      <c r="I72" s="36"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
       <c r="J72" s="7" t="s">
         <v>18</v>
       </c>
@@ -5206,17 +5001,16 @@
       <c r="AE72" s="3"/>
       <c r="AF72" s="3"/>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B73" s="2"/>
+    <row r="73" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="52">
+      <c r="E73" s="34"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="39">
         <v>14</v>
       </c>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
       <c r="J73" s="7" t="s">
         <v>16</v>
       </c>
@@ -5243,10 +5037,7 @@
       <c r="AE73" s="3"/>
       <c r="AF73" s="3"/>
     </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B74" s="2">
-        <v>47</v>
-      </c>
+    <row r="74" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C74" s="6">
         <v>1</v>
       </c>
@@ -5254,10 +5045,10 @@
       <c r="E74" s="21"/>
       <c r="F74" s="21"/>
       <c r="G74" s="21"/>
-      <c r="H74" s="35">
+      <c r="H74" s="56">
         <v>10</v>
       </c>
-      <c r="I74" s="35" t="s">
+      <c r="I74" s="56" t="s">
         <v>110</v>
       </c>
       <c r="J74" s="2" t="s">
@@ -5268,7 +5059,7 @@
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
@@ -5290,19 +5081,16 @@
       <c r="AE74" s="3"/>
       <c r="AF74" s="3"/>
     </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B75" s="2">
-        <v>48</v>
-      </c>
+    <row r="75" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="52">
-        <v>1</v>
-      </c>
-      <c r="H75" s="36"/>
-      <c r="I75" s="36"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="39">
+        <v>1</v>
+      </c>
+      <c r="H75" s="58"/>
+      <c r="I75" s="58"/>
       <c r="J75" s="2" t="s">
         <v>82</v>
       </c>
@@ -5330,19 +5118,16 @@
       <c r="AE75" s="3"/>
       <c r="AF75" s="3"/>
     </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B76" s="2">
-        <v>49</v>
-      </c>
+    <row r="76" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="52">
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="39">
         <v>2</v>
       </c>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36"/>
+      <c r="H76" s="58"/>
+      <c r="I76" s="58"/>
       <c r="J76" s="2" t="s">
         <v>91</v>
       </c>
@@ -5373,21 +5158,18 @@
       <c r="AE76" s="3"/>
       <c r="AF76" s="3"/>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B77" s="2">
-        <v>50</v>
-      </c>
+    <row r="77" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="52">
+      <c r="E77" s="34"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="39">
         <v>3</v>
       </c>
-      <c r="H77" s="36"/>
-      <c r="I77" s="36"/>
+      <c r="H77" s="58"/>
+      <c r="I77" s="58"/>
       <c r="J77" s="2" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="K77" s="26" t="s">
         <v>83</v>
@@ -5416,19 +5198,16 @@
       <c r="AE77" s="3"/>
       <c r="AF77" s="3"/>
     </row>
-    <row r="78" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B78" s="2">
-        <v>51</v>
-      </c>
+    <row r="78" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="52">
+      <c r="E78" s="34"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="39">
         <v>4</v>
       </c>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="H78" s="58"/>
+      <c r="I78" s="58"/>
       <c r="J78" s="13" t="s">
         <v>52</v>
       </c>
@@ -5459,19 +5238,16 @@
       <c r="AE78" s="3"/>
       <c r="AF78" s="3"/>
     </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B79" s="2">
-        <v>52</v>
-      </c>
+    <row r="79" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="52">
+      <c r="E79" s="34"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="39">
         <v>5</v>
       </c>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="H79" s="58"/>
+      <c r="I79" s="58"/>
       <c r="J79" s="14" t="s">
         <v>70</v>
       </c>
@@ -5502,19 +5278,16 @@
       <c r="AE79" s="3"/>
       <c r="AF79" s="3"/>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B80" s="2">
-        <v>53</v>
-      </c>
+    <row r="80" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="52">
+      <c r="E80" s="34"/>
+      <c r="F80" s="35"/>
+      <c r="G80" s="39">
         <v>6</v>
       </c>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="58"/>
       <c r="J80" s="17" t="s">
         <v>72</v>
       </c>
@@ -5545,19 +5318,16 @@
       <c r="AE80" s="3"/>
       <c r="AF80" s="3"/>
     </row>
-    <row r="81" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B81" s="2">
-        <v>54</v>
-      </c>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="52">
+      <c r="E81" s="34"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="39">
         <v>7</v>
       </c>
-      <c r="H81" s="36"/>
-      <c r="I81" s="36"/>
+      <c r="H81" s="58"/>
+      <c r="I81" s="58"/>
       <c r="J81" s="15" t="s">
         <v>53</v>
       </c>
@@ -5586,19 +5356,16 @@
       <c r="AE81" s="3"/>
       <c r="AF81" s="3"/>
     </row>
-    <row r="82" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B82" s="2">
-        <v>55</v>
-      </c>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
-      <c r="E82" s="47"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="52">
+      <c r="E82" s="34"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="39">
         <v>8</v>
       </c>
-      <c r="H82" s="36"/>
-      <c r="I82" s="36"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="58"/>
       <c r="J82" s="18" t="s">
         <v>54</v>
       </c>
@@ -5627,19 +5394,16 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
     </row>
-    <row r="83" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B83" s="2">
-        <v>56</v>
-      </c>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="52">
+      <c r="E83" s="34"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="39">
         <v>9</v>
       </c>
-      <c r="H83" s="36"/>
-      <c r="I83" s="36"/>
+      <c r="H83" s="58"/>
+      <c r="I83" s="58"/>
       <c r="J83" s="18" t="s">
         <v>77</v>
       </c>
@@ -5670,19 +5434,16 @@
       <c r="AE83" s="3"/>
       <c r="AF83" s="3"/>
     </row>
-    <row r="84" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B84" s="2">
-        <v>57</v>
-      </c>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="52">
+      <c r="E84" s="34"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="39">
         <v>10</v>
       </c>
-      <c r="H84" s="36"/>
-      <c r="I84" s="36"/>
+      <c r="H84" s="58"/>
+      <c r="I84" s="58"/>
       <c r="J84" s="12" t="s">
         <v>25</v>
       </c>
@@ -5711,19 +5472,16 @@
       <c r="AE84" s="3"/>
       <c r="AF84" s="3"/>
     </row>
-    <row r="85" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B85" s="2">
-        <v>58</v>
-      </c>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="52">
+      <c r="E85" s="34"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="39">
         <v>11</v>
       </c>
-      <c r="H85" s="36"/>
-      <c r="I85" s="36"/>
+      <c r="H85" s="58"/>
+      <c r="I85" s="58"/>
       <c r="J85" s="10" t="s">
         <v>26</v>
       </c>
@@ -5754,19 +5512,16 @@
       <c r="AE85" s="3"/>
       <c r="AF85" s="3"/>
     </row>
-    <row r="86" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B86" s="2">
-        <v>59</v>
-      </c>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
-      <c r="E86" s="47"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="52">
+      <c r="E86" s="34"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="39">
         <v>12</v>
       </c>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
       <c r="J86" s="11" t="s">
         <v>27</v>
       </c>
@@ -5797,17 +5552,16 @@
       <c r="AE86" s="3"/>
       <c r="AF86" s="3"/>
     </row>
-    <row r="87" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B87" s="40"/>
-      <c r="C87" s="42"/>
-      <c r="D87" s="42"/>
-      <c r="E87" s="42"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="42"/>
-      <c r="H87" s="42"/>
-      <c r="I87" s="42"/>
-      <c r="J87" s="42"/>
-      <c r="K87" s="41"/>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C87" s="46"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="46"/>
+      <c r="F87" s="46"/>
+      <c r="G87" s="46"/>
+      <c r="H87" s="46"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="46"/>
+      <c r="K87" s="47"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="3"/>
@@ -5830,18 +5584,15 @@
       <c r="AE87" s="3"/>
       <c r="AF87" s="3"/>
     </row>
-    <row r="88" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B88" s="2">
-        <v>60</v>
-      </c>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C88" s="6">
         <v>1</v>
       </c>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
-      <c r="F88" s="48"/>
+      <c r="F88" s="35"/>
       <c r="G88" s="21"/>
-      <c r="H88" s="35">
+      <c r="H88" s="56">
         <v>11</v>
       </c>
       <c r="I88" s="2" t="s">
@@ -5855,7 +5606,7 @@
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
@@ -5877,16 +5628,15 @@
       <c r="AE88" s="3"/>
       <c r="AF88" s="3"/>
     </row>
-    <row r="89" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B89" s="2">
-        <v>61</v>
-      </c>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
-      <c r="E89" s="47"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="52"/>
-      <c r="H89" s="36"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="39">
+        <v>1</v>
+      </c>
+      <c r="H89" s="58"/>
       <c r="I89" s="2" t="s">
         <v>123</v>
       </c>
@@ -5918,16 +5668,15 @@
       <c r="AE89" s="3"/>
       <c r="AF89" s="3"/>
     </row>
-    <row r="90" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B90" s="2">
-        <v>62</v>
-      </c>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="36"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="39">
+        <v>2</v>
+      </c>
+      <c r="H90" s="58"/>
       <c r="I90" s="2" t="s">
         <v>123</v>
       </c>
@@ -5959,16 +5708,15 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
     </row>
-    <row r="91" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B91" s="2">
-        <v>63</v>
-      </c>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
-      <c r="E91" s="47"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="52"/>
-      <c r="H91" s="36"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="39">
+        <v>3</v>
+      </c>
+      <c r="H91" s="58"/>
       <c r="I91" s="2" t="s">
         <v>123</v>
       </c>
@@ -6000,16 +5748,15 @@
       <c r="AE91" s="3"/>
       <c r="AF91" s="3"/>
     </row>
-    <row r="92" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B92" s="2">
-        <v>64</v>
-      </c>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="36"/>
+      <c r="E92" s="34"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="39">
+        <v>4</v>
+      </c>
+      <c r="H92" s="58"/>
       <c r="I92" s="2" t="s">
         <v>123</v>
       </c>
@@ -6041,16 +5788,15 @@
       <c r="AE92" s="3"/>
       <c r="AF92" s="3"/>
     </row>
-    <row r="93" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B93" s="2">
-        <v>65</v>
-      </c>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
-      <c r="E93" s="47"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="36"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="39">
+        <v>5</v>
+      </c>
+      <c r="H93" s="58"/>
       <c r="I93" s="2" t="s">
         <v>123</v>
       </c>
@@ -6082,16 +5828,15 @@
       <c r="AE93" s="3"/>
       <c r="AF93" s="3"/>
     </row>
-    <row r="94" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B94" s="2">
-        <v>66</v>
-      </c>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="36"/>
+      <c r="E94" s="34"/>
+      <c r="F94" s="35"/>
+      <c r="G94" s="39">
+        <v>6</v>
+      </c>
+      <c r="H94" s="58"/>
       <c r="I94" s="2" t="s">
         <v>123</v>
       </c>
@@ -6123,16 +5868,15 @@
       <c r="AE94" s="3"/>
       <c r="AF94" s="3"/>
     </row>
-    <row r="95" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B95" s="2">
-        <v>67</v>
-      </c>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
-      <c r="E95" s="47"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="36"/>
+      <c r="E95" s="34"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="39">
+        <v>7</v>
+      </c>
+      <c r="H95" s="58"/>
       <c r="I95" s="2" t="s">
         <v>123</v>
       </c>
@@ -6164,16 +5908,15 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
     </row>
-    <row r="96" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B96" s="2">
-        <v>68</v>
-      </c>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
-      <c r="E96" s="47"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="37"/>
+      <c r="E96" s="34"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="39">
+        <v>8</v>
+      </c>
+      <c r="H96" s="57"/>
       <c r="I96" s="2" t="s">
         <v>123</v>
       </c>
@@ -6205,17 +5948,16 @@
       <c r="AE96" s="3"/>
       <c r="AF96" s="3"/>
     </row>
-    <row r="97" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B97" s="40"/>
-      <c r="C97" s="42"/>
-      <c r="D97" s="42"/>
-      <c r="E97" s="42"/>
-      <c r="F97" s="42"/>
-      <c r="G97" s="42"/>
-      <c r="H97" s="42"/>
-      <c r="I97" s="42"/>
-      <c r="J97" s="42"/>
-      <c r="K97" s="41"/>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.25">
+      <c r="C97" s="46"/>
+      <c r="D97" s="46"/>
+      <c r="E97" s="46"/>
+      <c r="F97" s="46"/>
+      <c r="G97" s="46"/>
+      <c r="H97" s="46"/>
+      <c r="I97" s="46"/>
+      <c r="J97" s="46"/>
+      <c r="K97" s="47"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="3"/>
@@ -6238,22 +5980,19 @@
       <c r="AE97" s="3"/>
       <c r="AF97" s="3"/>
     </row>
-    <row r="98" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B98" s="2">
-        <v>69</v>
-      </c>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C98" s="6">
         <v>1</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="52"/>
+      <c r="F98" s="35"/>
+      <c r="G98" s="39"/>
       <c r="H98" s="3">
         <v>12</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>119</v>
@@ -6283,22 +6022,19 @@
       <c r="AE98" s="3"/>
       <c r="AF98" s="3"/>
     </row>
-    <row r="99" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B99" s="2">
-        <v>70</v>
-      </c>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C99" s="6">
         <v>1</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="52"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="39"/>
       <c r="H99" s="3">
         <v>13</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>117</v>
@@ -6328,22 +6064,19 @@
       <c r="AE99" s="3"/>
       <c r="AF99" s="3"/>
     </row>
-    <row r="100" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B100" s="2">
-        <v>71</v>
-      </c>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.25">
       <c r="C100" s="6">
         <v>1</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="52"/>
+      <c r="F100" s="35"/>
+      <c r="G100" s="39"/>
       <c r="H100" s="3">
         <v>14</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>121</v>
@@ -6374,10 +6107,10 @@
       <c r="AF100" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B87:K87"/>
+  <mergeCells count="34">
+    <mergeCell ref="C87:K87"/>
     <mergeCell ref="I74:I86"/>
-    <mergeCell ref="B97:K97"/>
+    <mergeCell ref="C97:K97"/>
     <mergeCell ref="H88:H96"/>
     <mergeCell ref="H74:H86"/>
     <mergeCell ref="H58:H73"/>
@@ -6387,22 +6120,21 @@
     <mergeCell ref="I19:I25"/>
     <mergeCell ref="H27:H39"/>
     <mergeCell ref="H41:H56"/>
-    <mergeCell ref="B57:K57"/>
-    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="C57:K57"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="H19:H25"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="I14:I17"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C18:K18"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="H14:H17"/>
-    <mergeCell ref="H19:H25"/>
     <mergeCell ref="M3:M5"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="N3:AF3"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="K3:K5"/>
     <mergeCell ref="L3:L5"/>
@@ -6435,10 +6167,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="56" t="s">
         <v>90</v>
       </c>
       <c r="D3" s="30" t="s">
@@ -6500,8 +6232,8 @@
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="30" t="s">
         <v>31</v>
       </c>
